--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25544.79</v>
+        <v>25413.54</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>143418.47</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>142163.53</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>24710.66</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24023.9</v>
+        <v>23986.66</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>73273.67999999999</v>
+        <v>73652.10000000001</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>37396.5</v>
+        <v>37601.01</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24520.46</v>
+        <v>24379.61</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39350.52</v>
+        <v>39181.48</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>42669.29</v>
+        <v>42404.75</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>64607.72</v>
+        <v>64901.15</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36977.88</v>
+        <v>37056.7</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>32858.35</v>
+        <v>33078.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4230-160-CM25</t>
+          <t>557970-21-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25413.54</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1340-9046-CM25</t>
+          <t>4230-160-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,32 +615,28 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>142633.04</v>
+        <v>25413.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1340-9047-CM25</t>
+          <t>1340-9046-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -680,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,13 +695,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>141384.98</v>
+        <v>142633.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4230-173-CM25</t>
+          <t>1340-9047-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,22 +716,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,28 +741,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>24888.81</v>
+        <v>141384.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1340-9067-CM25</t>
+          <t>4230-173-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23986.66</v>
+        <v>24888.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3853-803-CM25</t>
+          <t>1340-9067-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Automotriz Tecnosur Limitada</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>73652.10000000001</v>
+        <v>23986.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5592-3352-CM25</t>
+          <t>3853-803-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,27 +898,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42056.86</v>
+        <v>73652.10000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3623-1845-CM25</t>
+          <t>5592-3352-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -964,22 +964,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>37601.01</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5751-62-CM26</t>
+          <t>3623-1845-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,27 +1020,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1065,43 +1065,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24379.61</v>
+        <v>37601.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3623-216-CM26</t>
+          <t>5751-62-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39181.48</v>
+        <v>24379.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3573-46-CM26</t>
+          <t>3623-216-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.200.500-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>42404.75</v>
+        <v>39181.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3568-415-CM26</t>
+          <t>3573-46-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>64901.15</v>
+        <v>42404.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5418-159-CM26</t>
+          <t>3568-415-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1264,27 +1264,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>37056.7</v>
+        <v>64901.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>926853-51-CM26</t>
+          <t>5418-159-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1370,6 +1370,67 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
+        <v>37056.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>926853-51-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Valdivia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>33078.29</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>557970-21-CM25</t>
+          <t>5650-15-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27121.28</v>
+        <v>27138.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4230-160-CM25</t>
+          <t>4062-190-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25413.54</v>
+        <v>59339.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1340-9046-CM25</t>
+          <t>5751-79-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,32 +676,28 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>142633.04</v>
+        <v>26263.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1340-9047-CM25</t>
+          <t>1426100-43-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,32 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>141384.98</v>
+        <v>25556.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4230-173-CM25</t>
+          <t>4062-334-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -776,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24888.81</v>
+        <v>52470.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1340-9067-CM25</t>
+          <t>557970-21-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -837,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -867,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -882,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23986.66</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3853-803-CM25</t>
+          <t>4062-352-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -943,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>73652.10000000001</v>
+        <v>22660.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5592-3352-CM25</t>
+          <t>4062-355-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -974,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1004,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42056.86</v>
+        <v>28344.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3623-1845-CM25</t>
+          <t>4062-354-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1050,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1065,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>37601.01</v>
+        <v>24800.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5751-62-CM26</t>
+          <t>2282-100-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1081,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1126,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>24379.61</v>
+        <v>31048.32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3623-216-CM26</t>
+          <t>1271-23-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.200.500-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAFIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1172,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1187,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>39181.48</v>
+        <v>26380.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3573-46-CM26</t>
+          <t>5418-148-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1233,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1248,43 +1240,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>42404.75</v>
+        <v>73691.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3568-415-CM26</t>
+          <t>2910-162-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1309,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>64901.15</v>
+        <v>18303.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5418-159-CM26</t>
+          <t>1723-507-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1370,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37056.7</v>
+        <v>24018.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>926853-51-CM26</t>
+          <t>1497-141-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1431,7 +1423,1178 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
+        <v>34222.42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4697-24-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>161272.98</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1340-8976-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>69595.41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4230-160-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>25413.54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1340-9047-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>141384.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1340-9046-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>142633.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4230-173-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>24888.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1340-9067-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Automotriz Tecnosur Limitada</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>23986.66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3853-803-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>73652.10000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5592-3352-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>42056.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3623-1845-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.200.500-7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>37601.01</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5751-62-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>24379.61</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3623-216-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.200.500-7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAFIL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>39181.48</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3573-46-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>42404.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3568-415-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>64901.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5418-159-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>37056.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>926853-51-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>65.120.506-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Valdivia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>33078.29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4062-576-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.200.400-0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>29080.52</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4062-605-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.200.400-0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.262.067-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>27525.07</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4062-621-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.200.400-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>62193.77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4062-352-CM25</t>
+          <t>4062-354-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>22660.4</v>
+        <v>24800.36</v>
       </c>
     </row>
     <row r="9">
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4062-354-CM25</t>
+          <t>4062-352-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>24800.36</v>
+        <v>22660.4</v>
       </c>
     </row>
     <row r="11">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2595,6 +2595,67 @@
       </c>
       <c r="M35" s="2" t="n">
         <v>62193.77</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5612-180-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>39756.82</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1594,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1659,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1794,7 +1854,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1916,7 +1980,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1977,7 +2045,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2038,7 +2110,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2099,7 +2175,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2160,7 +2240,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2305,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2431,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2496,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2561,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2626,11 @@
           <t>77.262.067-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2691,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2756,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2768,6 +2768,71 @@
       </c>
       <c r="M36" s="2" t="n">
         <v>39756.82</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5751-263-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>28770.32</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-rios.xlsx
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
